--- a/MAJSushiConfig/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-vital-signs-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-vital-signs-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -476,7 +476,7 @@
     <t>author</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -581,7 +581,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -630,7 +630,7 @@
     <t>Observation.extension:author.extension:actor.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-organization-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-organization-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0)
 </t>
   </si>
   <si>
@@ -640,7 +640,7 @@
     <t>Observation.extension.url</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension</t>
   </si>
   <si>
     <t>Observation.extension:author.value[x]</t>
